--- a/Overpotnital/Air BP/BOL/Edited/CN Polyol 1.5bp air_edited.xlsx
+++ b/Overpotnital/Air BP/BOL/Edited/CN Polyol 1.5bp air_edited.xlsx
@@ -649,7 +649,7 @@
       <c r="D4" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F4" s="0">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.482</v>
+        <v>-0.485</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -739,7 +739,7 @@
       <c r="D5" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F5" s="0">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0456</v>
+        <v>-0.0439</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -821,7 +821,7 @@
       <c r="D6" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F6" s="0">
@@ -900,7 +900,7 @@
       <c r="D7" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F7" s="0">
@@ -983,7 +983,7 @@
       <c r="D8" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F8" s="0">
@@ -1057,7 +1057,7 @@
       <c r="D9" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F9" s="0">
@@ -1139,7 +1139,7 @@
       <c r="D10" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F10" s="0">
@@ -1213,7 +1213,7 @@
       <c r="D11" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F11" s="0">
@@ -1296,7 +1296,7 @@
       <c r="D12" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F12" s="0">
@@ -1374,7 +1374,7 @@
       <c r="D13" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F13" s="0">
@@ -1448,7 +1448,7 @@
       <c r="D14" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F14" s="0">
@@ -1522,7 +1522,7 @@
       <c r="D15" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F15" s="0">
@@ -1596,7 +1596,7 @@
       <c r="D16" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F16" s="0">
@@ -1670,7 +1670,7 @@
       <c r="D17" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F17" s="0">
@@ -1744,7 +1744,7 @@
       <c r="D18" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F18" s="0">
@@ -1818,7 +1818,7 @@
       <c r="D19" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F19" s="0">
@@ -1892,7 +1892,7 @@
       <c r="D20" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F20" s="0">
@@ -1966,7 +1966,7 @@
       <c r="D21" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F21" s="0">
@@ -2040,7 +2040,7 @@
       <c r="D22" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F22" s="0">
@@ -2114,7 +2114,7 @@
       <c r="D23" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F23" s="0">
@@ -2188,7 +2188,7 @@
       <c r="D24" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F24" s="0">
@@ -2262,7 +2262,7 @@
       <c r="D25" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F25" s="0">
@@ -2336,7 +2336,7 @@
       <c r="D26" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F26" s="0">
@@ -2410,7 +2410,7 @@
       <c r="D27" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F27" s="0">
@@ -2484,7 +2484,7 @@
       <c r="D28" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F28" s="0">
@@ -2558,7 +2558,7 @@
       <c r="D29" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F29" s="0">
@@ -2632,7 +2632,7 @@
       <c r="D30" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F30" s="0">
@@ -2706,7 +2706,7 @@
       <c r="D31" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F31" s="0">
@@ -2780,7 +2780,7 @@
       <c r="D32" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F32" s="0">
@@ -2847,7 +2847,7 @@
       <c r="D33" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F33" s="0">
@@ -2914,7 +2914,7 @@
       <c r="D34" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F34" s="0">
@@ -2981,7 +2981,7 @@
       <c r="D35" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F35" s="0">
@@ -3048,7 +3048,7 @@
       <c r="D36" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F36" s="0">
@@ -3115,7 +3115,7 @@
       <c r="D37" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F37" s="0">
@@ -3182,7 +3182,7 @@
       <c r="D38" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F38" s="0">
@@ -3249,7 +3249,7 @@
       <c r="D39" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F39" s="0">
@@ -3316,7 +3316,7 @@
       <c r="D40" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F40" s="0">
@@ -3383,7 +3383,7 @@
       <c r="D41" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F41" s="0">
@@ -3450,7 +3450,7 @@
       <c r="D42" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F42" s="0">
@@ -3517,7 +3517,7 @@
       <c r="D43" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F43" s="0">
@@ -3584,7 +3584,7 @@
       <c r="D44" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F44" s="0">
@@ -3651,7 +3651,7 @@
       <c r="D45" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F45" s="0">
@@ -3718,7 +3718,7 @@
       <c r="D46" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F46" s="0">
@@ -3785,7 +3785,7 @@
       <c r="D47" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F47" s="0">
@@ -3852,7 +3852,7 @@
       <c r="D48" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F48" s="0">
@@ -3919,7 +3919,7 @@
       <c r="D49" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F49" s="0">
@@ -3986,7 +3986,7 @@
       <c r="D50" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F50" s="0">
@@ -4053,7 +4053,7 @@
       <c r="D51" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F51" s="0">
@@ -4120,7 +4120,7 @@
       <c r="D52" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F52" s="0">
@@ -4187,7 +4187,7 @@
       <c r="D53" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F53" s="0">
@@ -4254,7 +4254,7 @@
       <c r="D54" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F54" s="0">
@@ -4315,7 +4315,7 @@
       <c r="D55" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F55" s="0">
@@ -4376,7 +4376,7 @@
       <c r="D56" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F56" s="0">
@@ -4437,7 +4437,7 @@
       <c r="D57" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F57" s="0">
@@ -4498,7 +4498,7 @@
       <c r="D58" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F58" s="0">
@@ -4559,7 +4559,7 @@
       <c r="D59" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F59" s="0">
@@ -4620,7 +4620,7 @@
       <c r="D60" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F60" s="0">
@@ -4681,7 +4681,7 @@
       <c r="D61" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F61" s="0">
@@ -4742,7 +4742,7 @@
       <c r="D62" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F62" s="0">
@@ -4803,7 +4803,7 @@
       <c r="D63" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F63" s="0">
@@ -4864,7 +4864,7 @@
       <c r="D64" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F64" s="0">
@@ -4925,7 +4925,7 @@
       <c r="D65" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F65" s="0">
@@ -4986,7 +4986,7 @@
       <c r="D66" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F66" s="0">
@@ -5047,7 +5047,7 @@
       <c r="D67" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F67" s="0">
@@ -5108,7 +5108,7 @@
       <c r="D68" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F68" s="0">
@@ -5169,7 +5169,7 @@
       <c r="D69" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F69" s="0">
@@ -5230,7 +5230,7 @@
       <c r="D70" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F70" s="0">
@@ -5291,7 +5291,7 @@
       <c r="D71" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F71" s="0">
@@ -5352,7 +5352,7 @@
       <c r="D72" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F72" s="0">
@@ -5413,7 +5413,7 @@
       <c r="D73" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F73" s="0">
@@ -5474,7 +5474,7 @@
       <c r="D74" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F74" s="0">
@@ -5535,7 +5535,7 @@
       <c r="D75" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F75" s="0">
@@ -5596,7 +5596,7 @@
       <c r="D76" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F76" s="0">
@@ -5657,7 +5657,7 @@
       <c r="D77" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F77" s="0">
@@ -5718,7 +5718,7 @@
       <c r="D78" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F78" s="0">
@@ -5779,7 +5779,7 @@
       <c r="D79" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F79" s="0">
@@ -5840,7 +5840,7 @@
       <c r="D80" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F80" s="0">
@@ -5901,7 +5901,7 @@
       <c r="D81" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F81" s="0">
@@ -5962,7 +5962,7 @@
       <c r="D82" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F82" s="0">
@@ -6023,7 +6023,7 @@
       <c r="D83" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F83" s="0">
@@ -6084,7 +6084,7 @@
       <c r="D84" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F84" s="0">
@@ -6145,7 +6145,7 @@
       <c r="D85" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F85" s="0">
@@ -6206,7 +6206,7 @@
       <c r="D86" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F86" s="0">
@@ -6267,7 +6267,7 @@
       <c r="D87" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F87" s="0">
@@ -6328,7 +6328,7 @@
       <c r="D88" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F88" s="0">
@@ -6389,7 +6389,7 @@
       <c r="D89" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F89" s="0">
@@ -6450,7 +6450,7 @@
       <c r="D90" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F90" s="0">
@@ -6511,7 +6511,7 @@
       <c r="D91" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F91" s="0">
@@ -6572,7 +6572,7 @@
       <c r="D92" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F92" s="0">
@@ -6633,7 +6633,7 @@
       <c r="D93" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F93" s="0">
@@ -6694,7 +6694,7 @@
       <c r="D94" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F94" s="0">
@@ -6755,7 +6755,7 @@
       <c r="D95" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F95" s="0">
@@ -6816,7 +6816,7 @@
       <c r="D96" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F96" s="0">
@@ -6877,7 +6877,7 @@
       <c r="D97" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F97" s="0">
@@ -6938,7 +6938,7 @@
       <c r="D98" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F98" s="0">
@@ -6999,7 +6999,7 @@
       <c r="D99" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F99" s="0">
@@ -7060,7 +7060,7 @@
       <c r="D100" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F100" s="0">
@@ -7121,7 +7121,7 @@
       <c r="D101" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F101" s="0">
@@ -7182,7 +7182,7 @@
       <c r="D102" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F102" s="0">
@@ -7243,7 +7243,7 @@
       <c r="D103" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F103" s="0">
@@ -7304,7 +7304,7 @@
       <c r="D104" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F104" s="0">
@@ -7365,7 +7365,7 @@
       <c r="D105" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F105" s="0">
@@ -7426,7 +7426,7 @@
       <c r="D106" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F106" s="0">
@@ -7487,7 +7487,7 @@
       <c r="D107" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F107" s="0">
@@ -7548,7 +7548,7 @@
       <c r="D108" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F108" s="0">
@@ -7609,7 +7609,7 @@
       <c r="D109" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F109" s="0">
@@ -7670,7 +7670,7 @@
       <c r="D110" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F110" s="0">
@@ -7731,7 +7731,7 @@
       <c r="D111" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F111" s="0">
@@ -7792,7 +7792,7 @@
       <c r="D112" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F112" s="0">
@@ -7853,7 +7853,7 @@
       <c r="D113" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F113" s="0">
@@ -7914,7 +7914,7 @@
       <c r="D114" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F114" s="0">
@@ -7975,7 +7975,7 @@
       <c r="D115" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F115" s="0">
@@ -8036,7 +8036,7 @@
       <c r="D116" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F116" s="0">
@@ -8097,7 +8097,7 @@
       <c r="D117" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F117" s="0">
@@ -8158,7 +8158,7 @@
       <c r="D118" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F118" s="0">
@@ -8219,7 +8219,7 @@
       <c r="D119" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F119" s="0">
@@ -8280,7 +8280,7 @@
       <c r="D120" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F120" s="0">
@@ -8341,7 +8341,7 @@
       <c r="D121" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F121" s="0">
@@ -8402,7 +8402,7 @@
       <c r="D122" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F122" s="0">
@@ -8463,7 +8463,7 @@
       <c r="D123" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F123" s="0">
@@ -8524,7 +8524,7 @@
       <c r="D124" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F124" s="0">
@@ -8585,7 +8585,7 @@
       <c r="D125" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F125" s="0">
@@ -8646,7 +8646,7 @@
       <c r="D126" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F126" s="0">
@@ -8707,7 +8707,7 @@
       <c r="D127" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F127" s="0">
@@ -8768,7 +8768,7 @@
       <c r="D128" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F128" s="0">
@@ -8829,7 +8829,7 @@
       <c r="D129" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F129" s="0">
@@ -8890,7 +8890,7 @@
       <c r="D130" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F130" s="0">
@@ -8951,7 +8951,7 @@
       <c r="D131" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F131" s="0">
@@ -9012,7 +9012,7 @@
       <c r="D132" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F132" s="0">
@@ -9073,7 +9073,7 @@
       <c r="D133" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F133" s="0">
@@ -9134,7 +9134,7 @@
       <c r="D134" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F134" s="0">
@@ -9195,7 +9195,7 @@
       <c r="D135" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F135" s="0">
@@ -9256,7 +9256,7 @@
       <c r="D136" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F136" s="0">
@@ -9317,7 +9317,7 @@
       <c r="D137" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F137" s="0">
@@ -9378,7 +9378,7 @@
       <c r="D138" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F138" s="0">
@@ -9439,7 +9439,7 @@
       <c r="D139" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F139" s="0">
@@ -9500,7 +9500,7 @@
       <c r="D140" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F140" s="0">
@@ -9554,7 +9554,7 @@
       <c r="D141" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F141" s="0">
@@ -9608,7 +9608,7 @@
       <c r="D142" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F142" s="0">
@@ -9662,7 +9662,7 @@
       <c r="D143" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F143" s="0">
@@ -9716,7 +9716,7 @@
       <c r="D144" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F144" s="0">
@@ -9770,7 +9770,7 @@
       <c r="D145" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F145" s="0">
@@ -9824,7 +9824,7 @@
       <c r="D146" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F146" s="0">
@@ -9878,7 +9878,7 @@
       <c r="D147" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F147" s="0">
@@ -9932,7 +9932,7 @@
       <c r="D148" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F148" s="0">
@@ -9986,7 +9986,7 @@
       <c r="D149" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F149" s="0">
@@ -10040,7 +10040,7 @@
       <c r="D150" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F150" s="0">
@@ -10094,7 +10094,7 @@
       <c r="D151" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F151" s="0">
@@ -10148,7 +10148,7 @@
       <c r="D152" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F152" s="0">
@@ -10202,7 +10202,7 @@
       <c r="D153" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F153" s="0">
@@ -10256,7 +10256,7 @@
       <c r="D154" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F154" s="0">
@@ -10310,7 +10310,7 @@
       <c r="D155" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F155" s="0">
@@ -10364,7 +10364,7 @@
       <c r="D156" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F156" s="0">
@@ -10418,7 +10418,7 @@
       <c r="D157" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F157" s="0">
@@ -10472,7 +10472,7 @@
       <c r="D158" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F158" s="0">
@@ -10526,7 +10526,7 @@
       <c r="D159" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F159" s="0">
@@ -10580,7 +10580,7 @@
       <c r="D160" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F160" s="0">
@@ -10634,7 +10634,7 @@
       <c r="D161" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F161" s="0">
@@ -10688,7 +10688,7 @@
       <c r="D162" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F162" s="0">
@@ -10742,7 +10742,7 @@
       <c r="D163" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F163" s="0">
@@ -10796,7 +10796,7 @@
       <c r="D164" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F164" s="0">
@@ -10850,7 +10850,7 @@
       <c r="D165" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F165" s="0">
@@ -10904,7 +10904,7 @@
       <c r="D166" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F166" s="0">
@@ -10958,7 +10958,7 @@
       <c r="D167" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F167" s="0">
@@ -11012,7 +11012,7 @@
       <c r="D168" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F168" s="0">
@@ -11066,7 +11066,7 @@
       <c r="D169" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F169" s="0">
@@ -11120,7 +11120,7 @@
       <c r="D170" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F170" s="0">
@@ -11174,7 +11174,7 @@
       <c r="D171" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F171" s="0">
@@ -11228,7 +11228,7 @@
       <c r="D172" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F172" s="0">
@@ -11282,7 +11282,7 @@
       <c r="D173" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F173" s="0">
@@ -11336,7 +11336,7 @@
       <c r="D174" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F174" s="0">
@@ -11390,7 +11390,7 @@
       <c r="D175" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F175" s="0">
@@ -11444,7 +11444,7 @@
       <c r="D176" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F176" s="0">
@@ -11498,7 +11498,7 @@
       <c r="D177" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F177" s="0">
@@ -11552,7 +11552,7 @@
       <c r="D178" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F178" s="0">
@@ -11606,7 +11606,7 @@
       <c r="D179" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F179" s="0">
@@ -11660,7 +11660,7 @@
       <c r="D180" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F180" s="0">
@@ -11714,7 +11714,7 @@
       <c r="D181" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F181" s="0">
@@ -11768,7 +11768,7 @@
       <c r="D182" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F182" s="0">
@@ -11822,7 +11822,7 @@
       <c r="D183" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F183" s="0">
@@ -11876,7 +11876,7 @@
       <c r="D184" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F184" s="0">
@@ -11930,7 +11930,7 @@
       <c r="D185" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F185" s="0">
@@ -11984,7 +11984,7 @@
       <c r="D186" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F186" s="0">
@@ -12038,7 +12038,7 @@
       <c r="D187" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F187" s="0">
@@ -12092,7 +12092,7 @@
       <c r="D188" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F188" s="0">
@@ -12146,7 +12146,7 @@
       <c r="D189" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F189" s="0">
@@ -12200,7 +12200,7 @@
       <c r="D190" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F190" s="0">
@@ -12254,7 +12254,7 @@
       <c r="D191" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F191" s="0">
@@ -12308,7 +12308,7 @@
       <c r="D192" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F192" s="0">
@@ -12362,7 +12362,7 @@
       <c r="D193" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E193" t="n">
+      <c r="E193" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F193" s="0">
@@ -12416,7 +12416,7 @@
       <c r="D194" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F194" s="0">
@@ -12470,7 +12470,7 @@
       <c r="D195" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F195" s="0">
@@ -12524,7 +12524,7 @@
       <c r="D196" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F196" s="0">
@@ -12578,7 +12578,7 @@
       <c r="D197" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F197" s="0">
@@ -12632,7 +12632,7 @@
       <c r="D198" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F198" s="0">
@@ -12686,7 +12686,7 @@
       <c r="D199" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F199" s="0">
@@ -12740,7 +12740,7 @@
       <c r="D200" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F200" s="0">
@@ -12794,7 +12794,7 @@
       <c r="D201" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F201" s="0">
@@ -12848,7 +12848,7 @@
       <c r="D202" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F202" s="0">
@@ -12902,7 +12902,7 @@
       <c r="D203" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F203" s="0">
@@ -12956,7 +12956,7 @@
       <c r="D204" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F204" s="0">
@@ -13010,7 +13010,7 @@
       <c r="D205" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E205" t="n">
+      <c r="E205" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F205" s="0">
@@ -13064,7 +13064,7 @@
       <c r="D206" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F206" s="0">
@@ -13118,7 +13118,7 @@
       <c r="D207" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F207" s="0">
@@ -13172,7 +13172,7 @@
       <c r="D208" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F208" s="0">
@@ -13226,7 +13226,7 @@
       <c r="D209" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F209" s="0">
@@ -13280,7 +13280,7 @@
       <c r="D210" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F210" s="0">
@@ -13334,7 +13334,7 @@
       <c r="D211" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F211" s="0">
@@ -13388,7 +13388,7 @@
       <c r="D212" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F212" s="0">
@@ -13442,7 +13442,7 @@
       <c r="D213" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F213" s="0">
@@ -13496,7 +13496,7 @@
       <c r="D214" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F214" s="0">
@@ -13550,7 +13550,7 @@
       <c r="D215" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F215" s="0">
@@ -13604,7 +13604,7 @@
       <c r="D216" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F216" s="0">
@@ -13658,7 +13658,7 @@
       <c r="D217" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F217" s="0">
@@ -13712,7 +13712,7 @@
       <c r="D218" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F218" s="0">
@@ -13766,7 +13766,7 @@
       <c r="D219" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F219" s="0">
@@ -13820,7 +13820,7 @@
       <c r="D220" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F220" s="0">
@@ -13874,7 +13874,7 @@
       <c r="D221" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F221" s="0">
@@ -13928,7 +13928,7 @@
       <c r="D222" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F222" s="0">
@@ -13982,7 +13982,7 @@
       <c r="D223" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E223" t="n">
+      <c r="E223" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F223" s="0">
@@ -14036,7 +14036,7 @@
       <c r="D224" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F224" s="0">
@@ -14090,7 +14090,7 @@
       <c r="D225" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F225" s="0">
@@ -14148,7 +14148,7 @@
       <c r="D226" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F226" s="0">
@@ -14202,7 +14202,7 @@
       <c r="D227" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F227" s="0">
@@ -14256,7 +14256,7 @@
       <c r="D228" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F228" s="0">
@@ -14310,7 +14310,7 @@
       <c r="D229" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E229" t="n">
+      <c r="E229" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F229" s="0">
@@ -14364,7 +14364,7 @@
       <c r="D230" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F230" s="0">
@@ -14418,7 +14418,7 @@
       <c r="D231" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F231" s="0">
@@ -14472,7 +14472,7 @@
       <c r="D232" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F232" s="0">
@@ -14526,7 +14526,7 @@
       <c r="D233" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F233" s="0">
@@ -14580,7 +14580,7 @@
       <c r="D234" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F234" s="0">
@@ -14634,7 +14634,7 @@
       <c r="D235" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F235" s="0">
@@ -14688,7 +14688,7 @@
       <c r="D236" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F236" s="0">
@@ -14742,7 +14742,7 @@
       <c r="D237" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F237" s="0">
@@ -14796,7 +14796,7 @@
       <c r="D238" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F238" s="0">
@@ -14850,7 +14850,7 @@
       <c r="D239" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F239" s="0">
@@ -14904,7 +14904,7 @@
       <c r="D240" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F240" s="0">
@@ -14958,7 +14958,7 @@
       <c r="D241" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F241" s="0">
@@ -15012,7 +15012,7 @@
       <c r="D242" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F242" s="0">
@@ -15066,7 +15066,7 @@
       <c r="D243" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F243" s="0">
@@ -15120,7 +15120,7 @@
       <c r="D244" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E244" t="n">
+      <c r="E244" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F244" s="0">
@@ -15174,7 +15174,7 @@
       <c r="D245" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F245" s="0">
@@ -15228,7 +15228,7 @@
       <c r="D246" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F246" s="0">
@@ -15282,7 +15282,7 @@
       <c r="D247" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F247" s="0">
@@ -15336,7 +15336,7 @@
       <c r="D248" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F248" s="0">
@@ -15390,7 +15390,7 @@
       <c r="D249" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F249" s="0">
@@ -15444,7 +15444,7 @@
       <c r="D250" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F250" s="0">
@@ -15498,7 +15498,7 @@
       <c r="D251" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F251" s="0">
@@ -15552,7 +15552,7 @@
       <c r="D252" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F252" s="0">
@@ -15606,7 +15606,7 @@
       <c r="D253" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F253" s="0">
@@ -15660,7 +15660,7 @@
       <c r="D254" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F254" s="0">
@@ -15714,7 +15714,7 @@
       <c r="D255" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F255" s="0">
@@ -15768,7 +15768,7 @@
       <c r="D256" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F256" s="0">
@@ -15822,7 +15822,7 @@
       <c r="D257" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F257" s="0">
@@ -15876,7 +15876,7 @@
       <c r="D258" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F258" s="0">
@@ -15930,7 +15930,7 @@
       <c r="D259" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F259" s="0">
@@ -15984,7 +15984,7 @@
       <c r="D260" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F260" s="0">
@@ -16038,7 +16038,7 @@
       <c r="D261" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F261" s="0">
@@ -16092,7 +16092,7 @@
       <c r="D262" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F262" s="0">
@@ -16146,7 +16146,7 @@
       <c r="D263" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E263" t="n">
+      <c r="E263" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F263" s="0">
@@ -16200,7 +16200,7 @@
       <c r="D264" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F264" s="0">
@@ -16254,7 +16254,7 @@
       <c r="D265" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F265" s="0">
@@ -16308,7 +16308,7 @@
       <c r="D266" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E266" t="n">
+      <c r="E266" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F266" s="0">
@@ -16362,7 +16362,7 @@
       <c r="D267" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E267" t="n">
+      <c r="E267" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F267" s="0">
@@ -16416,7 +16416,7 @@
       <c r="D268" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E268" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F268" s="0">
@@ -16470,7 +16470,7 @@
       <c r="D269" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E269" t="n">
+      <c r="E269" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F269" s="0">
@@ -16524,7 +16524,7 @@
       <c r="D270" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E270" t="n">
+      <c r="E270" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F270" s="0">
@@ -16578,7 +16578,7 @@
       <c r="D271" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E271" t="n">
+      <c r="E271" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F271" s="0">
@@ -16632,7 +16632,7 @@
       <c r="D272" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E272" t="n">
+      <c r="E272" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F272" s="0">
@@ -16686,7 +16686,7 @@
       <c r="D273" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E273" t="n">
+      <c r="E273" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F273" s="0">
@@ -16740,7 +16740,7 @@
       <c r="D274" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E274" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F274" s="0">
@@ -16794,7 +16794,7 @@
       <c r="D275" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E275" t="n">
+      <c r="E275" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F275" s="0">
@@ -16848,7 +16848,7 @@
       <c r="D276" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F276" s="0">
@@ -16902,7 +16902,7 @@
       <c r="D277" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E277" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F277" s="0">
@@ -16956,7 +16956,7 @@
       <c r="D278" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E278" t="n">
+      <c r="E278" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F278" s="0">
@@ -17010,7 +17010,7 @@
       <c r="D279" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E279" t="n">
+      <c r="E279" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F279" s="0">
@@ -17064,7 +17064,7 @@
       <c r="D280" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E280" t="n">
+      <c r="E280" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F280" s="0">
@@ -17118,7 +17118,7 @@
       <c r="D281" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E281" t="n">
+      <c r="E281" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F281" s="0">
@@ -17172,7 +17172,7 @@
       <c r="D282" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E282" t="n">
+      <c r="E282" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F282" s="0">
@@ -17226,7 +17226,7 @@
       <c r="D283" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E283" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F283" s="0">
@@ -17280,7 +17280,7 @@
       <c r="D284" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F284" s="0">
@@ -17334,7 +17334,7 @@
       <c r="D285" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E285" t="n">
+      <c r="E285" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F285" s="0">
@@ -17388,7 +17388,7 @@
       <c r="D286" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F286" s="0">
@@ -17442,7 +17442,7 @@
       <c r="D287" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E287" t="n">
+      <c r="E287" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F287" s="0">
@@ -17496,7 +17496,7 @@
       <c r="D288" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E288" t="n">
+      <c r="E288" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F288" s="0">
@@ -17550,7 +17550,7 @@
       <c r="D289" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E289" t="n">
+      <c r="E289" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F289" s="0">
@@ -17604,7 +17604,7 @@
       <c r="D290" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E290" t="n">
+      <c r="E290" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F290" s="0">
@@ -17658,7 +17658,7 @@
       <c r="D291" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E291" t="n">
+      <c r="E291" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F291" s="0">
@@ -17712,7 +17712,7 @@
       <c r="D292" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E292" t="n">
+      <c r="E292" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F292" s="0">
@@ -17766,7 +17766,7 @@
       <c r="D293" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E293" t="n">
+      <c r="E293" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F293" s="0">
@@ -17820,7 +17820,7 @@
       <c r="D294" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F294" s="0">
@@ -17874,7 +17874,7 @@
       <c r="D295" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F295" s="0">
@@ -17928,7 +17928,7 @@
       <c r="D296" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F296" s="0">
@@ -17982,7 +17982,7 @@
       <c r="D297" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F297" s="0">
@@ -18036,7 +18036,7 @@
       <c r="D298" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F298" s="0">
@@ -18090,7 +18090,7 @@
       <c r="D299" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F299" s="0">
@@ -18144,7 +18144,7 @@
       <c r="D300" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E300" t="n">
+      <c r="E300" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F300" s="0">
@@ -18198,7 +18198,7 @@
       <c r="D301" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E301" t="n">
+      <c r="E301" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F301" s="0">
@@ -18252,7 +18252,7 @@
       <c r="D302" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E302" t="n">
+      <c r="E302" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F302" s="0">
@@ -18306,7 +18306,7 @@
       <c r="D303" s="0" t="n">
         <v>0.0156</v>
       </c>
-      <c r="E303" t="n">
+      <c r="E303" s="0" t="n">
         <v>0.013</v>
       </c>
       <c r="F303" s="0">
@@ -18404,7 +18404,7 @@
       <c r="C2" s="0" t="n">
         <v>0.846</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>0.02188474498689175</v>
       </c>
       <c r="E2" s="0">
@@ -18439,7 +18439,7 @@
       <c r="C3" s="0" t="n">
         <v>0.837</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>0.0200420618057251</v>
       </c>
       <c r="E3" s="0">
@@ -18474,7 +18474,7 @@
       <c r="C4" s="0" t="n">
         <v>0.828</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>0.0202435664832592</v>
       </c>
       <c r="E4" s="0">
@@ -18509,7 +18509,7 @@
       <c r="C5" s="0" t="n">
         <v>0.8179999999999999</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.01856775023043156</v>
       </c>
       <c r="E5" s="0">
@@ -18544,7 +18544,7 @@
       <c r="C6" s="0" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.02292344346642494</v>
       </c>
       <c r="E6" s="0">
@@ -18579,7 +18579,7 @@
       <c r="C7" s="0" t="n">
         <v>0.803</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>0.02005913108587265</v>
       </c>
       <c r="E7" s="0">
@@ -18614,7 +18614,7 @@
       <c r="C8" s="0" t="n">
         <v>0.797</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>0.02002382278442383</v>
       </c>
       <c r="E8" s="0">
@@ -18649,7 +18649,7 @@
       <c r="C9" s="0" t="n">
         <v>0.791</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>0.02062098495662212</v>
       </c>
       <c r="E9" s="0">
@@ -18684,7 +18684,7 @@
       <c r="C10" s="0" t="n">
         <v>0.785</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>0.02150164172053337</v>
       </c>
       <c r="E10" s="0">
@@ -18719,7 +18719,7 @@
       <c r="C11" s="0" t="n">
         <v>0.779</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>0.02074512094259262</v>
       </c>
       <c r="E11" s="0">
@@ -18754,7 +18754,7 @@
       <c r="C12" s="0" t="n">
         <v>0.774</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>0.02223155833780766</v>
       </c>
       <c r="E12" s="0">
@@ -18789,7 +18789,7 @@
       <c r="C13" s="0" t="n">
         <v>0.768</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>0.02061885595321655</v>
       </c>
       <c r="E13" s="0">
@@ -18824,7 +18824,7 @@
       <c r="C14" s="0" t="n">
         <v>0.764</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>0.02157804369926453</v>
       </c>
       <c r="E14" s="0">
@@ -18859,7 +18859,7 @@
       <c r="C15" s="0" t="n">
         <v>0.759</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>0.02084491401910782</v>
       </c>
       <c r="E15" s="0">
@@ -18894,7 +18894,7 @@
       <c r="C16" s="0" t="n">
         <v>0.754</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>0.02178681455552578</v>
       </c>
       <c r="E16" s="0">
@@ -18929,7 +18929,7 @@
       <c r="C17" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>0.02149804309010506</v>
       </c>
       <c r="E17" s="0">
@@ -18964,7 +18964,7 @@
       <c r="C18" s="0" t="n">
         <v>0.746</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>0.02160311862826347</v>
       </c>
       <c r="E18" s="0">
@@ -18999,7 +18999,7 @@
       <c r="C19" s="0" t="n">
         <v>0.742</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>0.02212035283446312</v>
       </c>
       <c r="E19" s="0">
@@ -19034,7 +19034,7 @@
       <c r="C20" s="0" t="n">
         <v>0.737</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>0.02196707017719746</v>
       </c>
       <c r="E20" s="0">
@@ -19069,7 +19069,7 @@
       <c r="C21" s="0" t="n">
         <v>0.733</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>0.02210067585110664</v>
       </c>
       <c r="E21" s="0">
@@ -19104,7 +19104,7 @@
       <c r="C22" s="0" t="n">
         <v>0.729</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>0.02124469913542271</v>
       </c>
       <c r="E22" s="0">
@@ -19139,7 +19139,7 @@
       <c r="C23" s="0" t="n">
         <v>0.726</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.02223465405404568</v>
       </c>
       <c r="E23" s="0">
@@ -19174,7 +19174,7 @@
       <c r="C24" s="0" t="n">
         <v>0.722</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>0.02199913933873177</v>
       </c>
       <c r="E24" s="0">
@@ -19209,7 +19209,7 @@
       <c r="C25" s="0" t="n">
         <v>0.718</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>0.0226028598845005</v>
       </c>
       <c r="E25" s="0">
@@ -19244,7 +19244,7 @@
       <c r="C26" s="0" t="n">
         <v>0.714</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>0.02136674337089062</v>
       </c>
       <c r="E26" s="0">
@@ -19279,7 +19279,7 @@
       <c r="C27" s="0" t="n">
         <v>0.711</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>0.02244500815868378</v>
       </c>
       <c r="E27" s="0">
@@ -19314,7 +19314,7 @@
       <c r="C28" s="0" t="n">
         <v>0.707</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>0.02068980224430561</v>
       </c>
       <c r="E28" s="0">
@@ -19349,7 +19349,7 @@
       <c r="C29" s="0" t="n">
         <v>0.704</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>0.0218848567456007</v>
       </c>
       <c r="E29" s="0">
@@ -19384,7 +19384,7 @@
       <c r="C30" s="0" t="n">
         <v>0.701</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.02142326533794403</v>
       </c>
       <c r="E30" s="0">
@@ -19419,7 +19419,7 @@
       <c r="C31" s="0" t="n">
         <v>0.697</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>0.02206030488014221</v>
       </c>
       <c r="E31" s="0">
@@ -19454,7 +19454,7 @@
       <c r="C32" s="0" t="n">
         <v>0.694</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>0.02066031657159328</v>
       </c>
       <c r="E32" s="0">
@@ -19489,7 +19489,7 @@
       <c r="C33" s="0" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>0.02202636934816837</v>
       </c>
       <c r="E33" s="0">
@@ -19524,7 +19524,7 @@
       <c r="C34" s="0" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>0.02086247317492962</v>
       </c>
       <c r="E34" s="0">
@@ -19559,7 +19559,7 @@
       <c r="C35" s="0" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0.02169629000127316</v>
       </c>
       <c r="E35" s="0">
@@ -19594,7 +19594,7 @@
       <c r="C36" s="0" t="n">
         <v>0.681</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0.02072627283632755</v>
       </c>
       <c r="E36" s="0">
@@ -19629,7 +19629,7 @@
       <c r="C37" s="0" t="n">
         <v>0.678</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0.02208458632230759</v>
       </c>
       <c r="E37" s="0">
@@ -19664,7 +19664,7 @@
       <c r="C38" s="0" t="n">
         <v>0.675</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0.02080466970801353</v>
       </c>
       <c r="E38" s="0">
@@ -19699,7 +19699,7 @@
       <c r="C39" s="0" t="n">
         <v>0.672</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>0.02198246121406555</v>
       </c>
       <c r="E39" s="0">
@@ -19734,7 +19734,7 @@
       <c r="C40" s="0" t="n">
         <v>0.669</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>0.0207621343433857</v>
       </c>
       <c r="E40" s="0">
@@ -19769,7 +19769,7 @@
       <c r="C41" s="0" t="n">
         <v>0.666</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>0.02174874022603035</v>
       </c>
       <c r="E41" s="0">
@@ -19804,7 +19804,7 @@
       <c r="C42" s="0" t="n">
         <v>0.663</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.02079889923334122</v>
       </c>
       <c r="E42" s="0">
@@ -19839,7 +19839,7 @@
       <c r="C43" s="0" t="n">
         <v>0.66</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>0.02128463797271252</v>
       </c>
       <c r="E43" s="0">
@@ -19874,7 +19874,7 @@
       <c r="C44" s="0" t="n">
         <v>0.657</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>0.02105836756527424</v>
       </c>
       <c r="E44" s="0">
@@ -19909,7 +19909,7 @@
       <c r="C45" s="0" t="n">
         <v>0.654</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>0.02128434740006924</v>
       </c>
       <c r="E45" s="0">
@@ -19944,7 +19944,7 @@
       <c r="C46" s="0" t="n">
         <v>0.651</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>0.02171558514237404</v>
       </c>
       <c r="E46" s="0">
@@ -19979,7 +19979,7 @@
       <c r="C47" s="0" t="n">
         <v>0.648</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>0.02162325009703636</v>
       </c>
       <c r="E47" s="0">
@@ -20014,7 +20014,7 @@
       <c r="C48" s="0" t="n">
         <v>0.646</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0.02090091444551945</v>
       </c>
       <c r="E48" s="0">
@@ -20049,7 +20049,7 @@
       <c r="C49" s="0" t="n">
         <v>0.643</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0.02139896526932716</v>
       </c>
       <c r="E49" s="0">
@@ -20084,7 +20084,7 @@
       <c r="C50" s="0" t="n">
         <v>0.64</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0.02111426182091236</v>
       </c>
       <c r="E50" s="0">
@@ -20119,7 +20119,7 @@
       <c r="C51" s="0" t="n">
         <v>0.637</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0.02089146338403225</v>
       </c>
       <c r="E51" s="0">
@@ -20154,7 +20154,7 @@
       <c r="C52" s="0" t="n">
         <v>0.634</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0.02088642492890358</v>
       </c>
       <c r="E52" s="0">
@@ -20189,7 +20189,7 @@
       <c r="C53" s="0" t="n">
         <v>0.631</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.02163968607783318</v>
       </c>
       <c r="E53" s="0">
@@ -20224,7 +20224,7 @@
       <c r="C54" s="0" t="n">
         <v>0.629</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.0208536833524704</v>
       </c>
       <c r="E54" s="0">
@@ -20259,7 +20259,7 @@
       <c r="C55" s="0" t="n">
         <v>0.626</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.02042403817176819</v>
       </c>
       <c r="E55" s="0">
@@ -20294,7 +20294,7 @@
       <c r="C56" s="0" t="n">
         <v>0.623</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.02127382904291153</v>
       </c>
       <c r="E56" s="0">
@@ -20329,7 +20329,7 @@
       <c r="C57" s="0" t="n">
         <v>0.621</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0.02156965248286724</v>
       </c>
       <c r="E57" s="0">
@@ -20364,7 +20364,7 @@
       <c r="C58" s="0" t="n">
         <v>0.618</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.0206918828189373</v>
       </c>
       <c r="E58" s="0">
@@ -20399,7 +20399,7 @@
       <c r="C59" s="0" t="n">
         <v>0.615</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0.02107076346874237</v>
       </c>
       <c r="E59" s="0">
@@ -20434,7 +20434,7 @@
       <c r="C60" s="0" t="n">
         <v>0.613</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0.02087909355759621</v>
       </c>
       <c r="E60" s="0">
@@ -20469,7 +20469,7 @@
       <c r="C61" s="0" t="n">
         <v>0.61</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>0.02139941975474358</v>
       </c>
       <c r="E61" s="0">
@@ -20504,7 +20504,7 @@
       <c r="C62" s="0" t="n">
         <v>0.608</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>0.02168705686926842</v>
       </c>
       <c r="E62" s="0">
@@ -20539,7 +20539,7 @@
       <c r="C63" s="0" t="n">
         <v>0.605</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>0.02088871784508228</v>
       </c>
       <c r="E63" s="0">
@@ -20574,7 +20574,7 @@
       <c r="C64" s="0" t="n">
         <v>0.603</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0.02038130722939968</v>
       </c>
       <c r="E64" s="0">
@@ -20609,7 +20609,7 @@
       <c r="C65" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0.02090147696435452</v>
       </c>
       <c r="E65" s="0">
@@ -20644,7 +20644,7 @@
       <c r="C66" s="0" t="n">
         <v>0.597</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0.02089935913681984</v>
       </c>
       <c r="E66" s="0">
@@ -20679,7 +20679,7 @@
       <c r="C67" s="0" t="n">
         <v>0.595</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0.02123693376779556</v>
       </c>
       <c r="E67" s="0">
@@ -20714,7 +20714,7 @@
       <c r="C68" s="0" t="n">
         <v>0.592</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0.02121633850038052</v>
       </c>
       <c r="E68" s="0">
@@ -20749,7 +20749,7 @@
       <c r="C69" s="0" t="n">
         <v>0.59</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0.02192088775336742</v>
       </c>
       <c r="E69" s="0">
@@ -20784,7 +20784,7 @@
       <c r="C70" s="0" t="n">
         <v>0.587</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.02134180627763271</v>
       </c>
       <c r="E70" s="0">
@@ -20819,7 +20819,7 @@
       <c r="C71" s="0" t="n">
         <v>0.585</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.02118257060647011</v>
       </c>
       <c r="E71" s="0">
@@ -20854,7 +20854,7 @@
       <c r="C72" s="0" t="n">
         <v>0.582</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0.02070923149585724</v>
       </c>
       <c r="E72" s="0">
@@ -20889,7 +20889,7 @@
       <c r="C73" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0.02084982767701149</v>
       </c>
       <c r="E73" s="0">
@@ -20924,7 +20924,7 @@
       <c r="C74" s="0" t="n">
         <v>0.578</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0.02178002707660198</v>
       </c>
       <c r="E74" s="0">
@@ -20959,7 +20959,7 @@
       <c r="C75" s="0" t="n">
         <v>0.575</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.0216306746006012</v>
       </c>
       <c r="E75" s="0">
@@ -20994,7 +20994,7 @@
       <c r="C76" s="0" t="n">
         <v>0.573</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0.0215228870511055</v>
       </c>
       <c r="E76" s="0">
@@ -21029,7 +21029,7 @@
       <c r="C77" s="0" t="n">
         <v>0.57</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.02099636942148209</v>
       </c>
       <c r="E77" s="0">
@@ -21064,7 +21064,7 @@
       <c r="C78" s="0" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>0.02120652794837952</v>
       </c>
       <c r="E78" s="0">
@@ -21099,7 +21099,7 @@
       <c r="C79" s="0" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>0.02128704264760017</v>
       </c>
       <c r="E79" s="0">
@@ -21134,7 +21134,7 @@
       <c r="C80" s="0" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="0" t="n">
         <v>0.0215698704123497</v>
       </c>
       <c r="E80" s="0">
@@ -21169,7 +21169,7 @@
       <c r="C81" s="0" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="0" t="n">
         <v>0.02135146409273148</v>
       </c>
       <c r="E81" s="0">
@@ -21204,7 +21204,7 @@
       <c r="C82" s="0" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="0" t="n">
         <v>0.02219929546117783</v>
       </c>
       <c r="E82" s="0">
@@ -21239,7 +21239,7 @@
       <c r="C83" s="0" t="n">
         <v>0.556</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="0" t="n">
         <v>0.02134930714964867</v>
       </c>
       <c r="E83" s="0">
@@ -21274,7 +21274,7 @@
       <c r="C84" s="0" t="n">
         <v>0.554</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.0212129782885313</v>
       </c>
       <c r="E84" s="0">
@@ -21309,7 +21309,7 @@
       <c r="C85" s="0" t="n">
         <v>0.551</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="0" t="n">
         <v>0.02233623340725899</v>
       </c>
       <c r="E85" s="0">
@@ -21344,7 +21344,7 @@
       <c r="C86" s="0" t="n">
         <v>0.549</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="0" t="n">
         <v>0.0209533553570509</v>
       </c>
       <c r="E86" s="0">
@@ -21379,7 +21379,7 @@
       <c r="C87" s="0" t="n">
         <v>0.546</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="0" t="n">
         <v>0.02204925194382668</v>
       </c>
       <c r="E87" s="0">
@@ -21414,7 +21414,7 @@
       <c r="C88" s="0" t="n">
         <v>0.544</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="0" t="n">
         <v>0.02171573415398598</v>
       </c>
       <c r="E88" s="0">
@@ -21449,7 +21449,7 @@
       <c r="C89" s="0" t="n">
         <v>0.542</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="0" t="n">
         <v>0.0216961745172739</v>
       </c>
       <c r="E89" s="0">
@@ -21484,7 +21484,7 @@
       <c r="C90" s="0" t="n">
         <v>0.539</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="0" t="n">
         <v>0.02190676517784595</v>
       </c>
       <c r="E90" s="0">
@@ -21519,7 +21519,7 @@
       <c r="C91" s="0" t="n">
         <v>0.537</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="0" t="n">
         <v>0.02175609022378922</v>
       </c>
       <c r="E91" s="0">
@@ -21554,7 +21554,7 @@
       <c r="C92" s="0" t="n">
         <v>0.534</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="0" t="n">
         <v>0.02242948859930038</v>
       </c>
       <c r="E92" s="0">
@@ -21589,7 +21589,7 @@
       <c r="C93" s="0" t="n">
         <v>0.533</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>0.0215414147824049</v>
       </c>
       <c r="E93" s="0">
@@ -21624,7 +21624,7 @@
       <c r="C94" s="0" t="n">
         <v>0.53</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.02252337895333767</v>
       </c>
       <c r="E94" s="0">
@@ -21659,7 +21659,7 @@
       <c r="C95" s="0" t="n">
         <v>0.528</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>0.02160502783954144</v>
       </c>
       <c r="E95" s="0">
@@ -21694,7 +21694,7 @@
       <c r="C96" s="0" t="n">
         <v>0.526</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.02235906384885311</v>
       </c>
       <c r="E96" s="0">
@@ -21729,7 +21729,7 @@
       <c r="C97" s="0" t="n">
         <v>0.524</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="0" t="n">
         <v>0.0217084027826786</v>
       </c>
       <c r="E97" s="0">
@@ -21764,7 +21764,7 @@
       <c r="C98" s="0" t="n">
         <v>0.521</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="0" t="n">
         <v>0.02225402183830738</v>
       </c>
       <c r="E98" s="0">
@@ -21799,7 +21799,7 @@
       <c r="C99" s="0" t="n">
         <v>0.519</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>0.02203675732016563</v>
       </c>
       <c r="E99" s="0">
@@ -21834,7 +21834,7 @@
       <c r="C100" s="0" t="n">
         <v>0.517</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="0" t="n">
         <v>0.02238716930150986</v>
       </c>
       <c r="E100" s="0">
@@ -21869,7 +21869,7 @@
       <c r="C101" s="0" t="n">
         <v>0.514</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.02200327999889851</v>
       </c>
       <c r="E101" s="0">
@@ -21904,7 +21904,7 @@
       <c r="C102" s="0" t="n">
         <v>0.512</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="0" t="n">
         <v>0.02229078486561775</v>
       </c>
       <c r="E102" s="0">
@@ -21939,7 +21939,7 @@
       <c r="C103" s="0" t="n">
         <v>0.51</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0.02204912714660168</v>
       </c>
       <c r="E103" s="0">
@@ -21974,7 +21974,7 @@
       <c r="C104" s="0" t="n">
         <v>0.508</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="0" t="n">
         <v>0.02202761545777321</v>
       </c>
       <c r="E104" s="0">
@@ -22009,7 +22009,7 @@
       <c r="C105" s="0" t="n">
         <v>0.506</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="0" t="n">
         <v>0.02176796086132526</v>
       </c>
       <c r="E105" s="0">
@@ -22044,7 +22044,7 @@
       <c r="C106" s="0" t="n">
         <v>0.503</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="0" t="n">
         <v>0.02218662574887276</v>
       </c>
       <c r="E106" s="0">
@@ -22079,7 +22079,7 @@
       <c r="C107" s="0" t="n">
         <v>0.501</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="0" t="n">
         <v>0.02234361320734024</v>
       </c>
       <c r="E107" s="0">
@@ -22114,7 +22114,7 @@
       <c r="C108" s="0" t="n">
         <v>0.499</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="0" t="n">
         <v>0.02194085530936718</v>
       </c>
       <c r="E108" s="0">
@@ -22149,7 +22149,7 @@
       <c r="C109" s="0" t="n">
         <v>0.496</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0.02266308106482029</v>
       </c>
       <c r="E109" s="0">
@@ -22184,7 +22184,7 @@
       <c r="C110" s="0" t="n">
         <v>0.494</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.02264226041734219</v>
       </c>
       <c r="E110" s="0">
@@ -22219,7 +22219,7 @@
       <c r="C111" s="0" t="n">
         <v>0.492</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="0" t="n">
         <v>0.02145604602992535</v>
       </c>
       <c r="E111" s="0">
@@ -22254,7 +22254,7 @@
       <c r="C112" s="0" t="n">
         <v>0.49</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="0" t="n">
         <v>0.02272169478237629</v>
       </c>
       <c r="E112" s="0">
@@ -22289,7 +22289,7 @@
       <c r="C113" s="0" t="n">
         <v>0.488</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.02283627167344093</v>
       </c>
       <c r="E113" s="0">
@@ -22324,7 +22324,7 @@
       <c r="C114" s="0" t="n">
         <v>0.485</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="0" t="n">
         <v>0.02256097830832005</v>
       </c>
       <c r="E114" s="0">
@@ -22359,7 +22359,7 @@
       <c r="C115" s="0" t="n">
         <v>0.483</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="0" t="n">
         <v>0.02283190004527569</v>
       </c>
       <c r="E115" s="0">
@@ -22394,7 +22394,7 @@
       <c r="C116" s="0" t="n">
         <v>0.481</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="0" t="n">
         <v>0.02224512957036495</v>
       </c>
       <c r="E116" s="0">
@@ -22429,7 +22429,7 @@
       <c r="C117" s="0" t="n">
         <v>0.479</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="0" t="n">
         <v>0.02277129143476486</v>
       </c>
       <c r="E117" s="0">
@@ -22464,7 +22464,7 @@
       <c r="C118" s="0" t="n">
         <v>0.477</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="0" t="n">
         <v>0.02282169088721275</v>
       </c>
       <c r="E118" s="0">
@@ -22499,7 +22499,7 @@
       <c r="C119" s="0" t="n">
         <v>0.474</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="0" t="n">
         <v>0.02233251929283142</v>
       </c>
       <c r="E119" s="0">
@@ -22534,7 +22534,7 @@
       <c r="C120" s="0" t="n">
         <v>0.473</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="0" t="n">
         <v>0.02308384887874126</v>
       </c>
       <c r="E120" s="0">
@@ -22569,7 +22569,7 @@
       <c r="C121" s="0" t="n">
         <v>0.47</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="0" t="n">
         <v>0.02248584665358067</v>
       </c>
       <c r="E121" s="0">
@@ -22604,7 +22604,7 @@
       <c r="C122" s="0" t="n">
         <v>0.468</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="0" t="n">
         <v>0.02315918728709221</v>
       </c>
       <c r="E122" s="0">
@@ -22639,7 +22639,7 @@
       <c r="C123" s="0" t="n">
         <v>0.466</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="0" t="n">
         <v>0.02308138087391853</v>
       </c>
       <c r="E123" s="0">
@@ -22674,7 +22674,7 @@
       <c r="C124" s="0" t="n">
         <v>0.464</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="0" t="n">
         <v>0.02228741347789764</v>
       </c>
       <c r="E124" s="0">
@@ -22709,7 +22709,7 @@
       <c r="C125" s="0" t="n">
         <v>0.462</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="0" t="n">
         <v>0.02303110808134079</v>
       </c>
       <c r="E125" s="0">
@@ -22744,7 +22744,7 @@
       <c r="C126" s="0" t="n">
         <v>0.46</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.02348831482231617</v>
       </c>
       <c r="E126" s="0">
@@ -22779,7 +22779,7 @@
       <c r="C127" s="0" t="n">
         <v>0.458</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.02262923307716846</v>
       </c>
       <c r="E127" s="0">
@@ -22814,7 +22814,7 @@
       <c r="C128" s="0" t="n">
         <v>0.455</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="0" t="n">
         <v>0.02375646680593491</v>
       </c>
       <c r="E128" s="0">
@@ -22849,7 +22849,7 @@
       <c r="C129" s="0" t="n">
         <v>0.453</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="0" t="n">
         <v>0.02298040315508842</v>
       </c>
       <c r="E129" s="0">
@@ -22884,7 +22884,7 @@
       <c r="C130" s="0" t="n">
         <v>0.451</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="0" t="n">
         <v>0.0228426568210125</v>
       </c>
       <c r="E130" s="0">
@@ -22919,7 +22919,7 @@
       <c r="C131" s="0" t="n">
         <v>0.449</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="0" t="n">
         <v>0.02334821410477161</v>
       </c>
       <c r="E131" s="0">
@@ -22954,7 +22954,7 @@
       <c r="C132" s="0" t="n">
         <v>0.447</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="0" t="n">
         <v>0.02255835197865963</v>
       </c>
       <c r="E132" s="0">
@@ -22989,7 +22989,7 @@
       <c r="C133" s="0" t="n">
         <v>0.445</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="0" t="n">
         <v>0.02312240190804005</v>
       </c>
       <c r="E133" s="0">
@@ -23024,7 +23024,7 @@
       <c r="C134" s="0" t="n">
         <v>0.443</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="0" t="n">
         <v>0.02291266620159149</v>
       </c>
       <c r="E134" s="0">
@@ -23059,7 +23059,7 @@
       <c r="C135" s="0" t="n">
         <v>0.441</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="0" t="n">
         <v>0.023176034912467</v>
       </c>
       <c r="E135" s="0">
@@ -23094,7 +23094,7 @@
       <c r="C136" s="0" t="n">
         <v>0.439</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="0" t="n">
         <v>0.02292532101273537</v>
       </c>
       <c r="E136" s="0">
@@ -23129,7 +23129,7 @@
       <c r="C137" s="0" t="n">
         <v>0.437</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="0" t="n">
         <v>0.02327945083379745</v>
       </c>
       <c r="E137" s="0">
@@ -23164,7 +23164,7 @@
       <c r="C138" s="0" t="n">
         <v>0.434</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="0" t="n">
         <v>0.02313651889562607</v>
       </c>
       <c r="E138" s="0">
@@ -23199,7 +23199,7 @@
       <c r="C139" s="0" t="n">
         <v>0.432</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="0" t="n">
         <v>0.02359609119594097</v>
       </c>
       <c r="E139" s="0">
@@ -23234,7 +23234,7 @@
       <c r="C140" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="0" t="n">
         <v>0.02316553890705109</v>
       </c>
       <c r="E140" s="0">
@@ -23269,7 +23269,7 @@
       <c r="C141" s="0" t="n">
         <v>0.428</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="0" t="n">
         <v>0.02403800003230572</v>
       </c>
       <c r="E141" s="0">
@@ -23304,7 +23304,7 @@
       <c r="C142" s="0" t="n">
         <v>0.426</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="0" t="n">
         <v>0.0228748694062233</v>
       </c>
       <c r="E142" s="0">
@@ -23339,7 +23339,7 @@
       <c r="C143" s="0" t="n">
         <v>0.424</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="0" t="n">
         <v>0.02321753092110157</v>
       </c>
       <c r="E143" s="0">
@@ -23374,7 +23374,7 @@
       <c r="C144" s="0" t="n">
         <v>0.422</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="0" t="n">
         <v>0.02334983088076115</v>
       </c>
       <c r="E144" s="0">
@@ -23409,7 +23409,7 @@
       <c r="C145" s="0" t="n">
         <v>0.42</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="0" t="n">
         <v>0.02308961376547813</v>
       </c>
       <c r="E145" s="0">
@@ -23444,7 +23444,7 @@
       <c r="C146" s="0" t="n">
         <v>0.418</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="0" t="n">
         <v>0.02444537356495857</v>
       </c>
       <c r="E146" s="0">
@@ -23479,7 +23479,7 @@
       <c r="C147" s="0" t="n">
         <v>0.416</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="0" t="n">
         <v>0.02307135425508022</v>
       </c>
       <c r="E147" s="0">
@@ -23514,7 +23514,7 @@
       <c r="C148" s="0" t="n">
         <v>0.413</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="0" t="n">
         <v>0.02379290014505386</v>
       </c>
       <c r="E148" s="0">
@@ -23549,7 +23549,7 @@
       <c r="C149" s="0" t="n">
         <v>0.411</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="0" t="n">
         <v>0.02341685071587563</v>
       </c>
       <c r="E149" s="0">
@@ -23584,7 +23584,7 @@
       <c r="C150" s="0" t="n">
         <v>0.409</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="0" t="n">
         <v>0.02343933098018169</v>
       </c>
       <c r="E150" s="0">
@@ -23619,7 +23619,7 @@
       <c r="C151" s="0" t="n">
         <v>0.407</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="0" t="n">
         <v>0.02361765690147877</v>
       </c>
       <c r="E151" s="0">
@@ -23654,7 +23654,7 @@
       <c r="C152" s="0" t="n">
         <v>0.405</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="0" t="n">
         <v>0.02412284165620804</v>
       </c>
       <c r="E152" s="0">
@@ -23689,7 +23689,7 @@
       <c r="C153" s="0" t="n">
         <v>0.403</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="0" t="n">
         <v>0.02367998659610748</v>
       </c>
       <c r="E153" s="0">
@@ -23724,7 +23724,7 @@
       <c r="C154" s="0" t="n">
         <v>0.401</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="0" t="n">
         <v>0.02378236874938011</v>
       </c>
       <c r="E154" s="0">
@@ -23759,7 +23759,7 @@
       <c r="C155" s="0" t="n">
         <v>0.399</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="0" t="n">
         <v>0.02381190285086632</v>
       </c>
       <c r="E155" s="0">
@@ -23794,7 +23794,7 @@
       <c r="C156" s="0" t="n">
         <v>0.397</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="0" t="n">
         <v>0.02335663884878159</v>
       </c>
       <c r="E156" s="0">
@@ -23829,7 +23829,7 @@
       <c r="C157" s="0" t="n">
         <v>0.395</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="0" t="n">
         <v>0.02376625686883926</v>
       </c>
       <c r="E157" s="0">
@@ -23864,7 +23864,7 @@
       <c r="C158" s="0" t="n">
         <v>0.393</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="0" t="n">
         <v>0.02348150312900543</v>
       </c>
       <c r="E158" s="0">
@@ -23899,7 +23899,7 @@
       <c r="C159" s="0" t="n">
         <v>0.39</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="0" t="n">
         <v>0.02421257458627224</v>
       </c>
       <c r="E159" s="0">
@@ -23934,7 +23934,7 @@
       <c r="C160" s="0" t="n">
         <v>0.388</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="0" t="n">
         <v>0.02338164113461971</v>
       </c>
       <c r="E160" s="0">
@@ -23969,7 +23969,7 @@
       <c r="C161" s="0" t="n">
         <v>0.386</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="0" t="n">
         <v>0.02417968027293682</v>
       </c>
       <c r="E161" s="0">
@@ -24004,7 +24004,7 @@
       <c r="C162" s="0" t="n">
         <v>0.384</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="0" t="n">
         <v>0.02359800599515438</v>
       </c>
       <c r="E162" s="0">
@@ -24039,7 +24039,7 @@
       <c r="C163" s="0" t="n">
         <v>0.382</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="0" t="n">
         <v>0.02405710332095623</v>
       </c>
       <c r="E163" s="0">
@@ -24074,7 +24074,7 @@
       <c r="C164" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="0" t="n">
         <v>0.02362007275223732</v>
       </c>
       <c r="E164" s="0">
@@ -24109,7 +24109,7 @@
       <c r="C165" s="0" t="n">
         <v>0.378</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="0" t="n">
         <v>0.02441132627427578</v>
       </c>
       <c r="E165" s="0">
@@ -24144,7 +24144,7 @@
       <c r="C166" s="0" t="n">
         <v>0.375</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="0" t="n">
         <v>0.02377547696232796</v>
       </c>
       <c r="E166" s="0">
@@ -24179,7 +24179,7 @@
       <c r="C167" s="0" t="n">
         <v>0.373</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="0" t="n">
         <v>0.02424614503979683</v>
       </c>
       <c r="E167" s="0">
@@ -24214,7 +24214,7 @@
       <c r="C168" s="0" t="n">
         <v>0.371</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="0" t="n">
         <v>0.02394500561058521</v>
       </c>
       <c r="E168" s="0">
@@ -24249,7 +24249,7 @@
       <c r="C169" s="0" t="n">
         <v>0.369</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="0" t="n">
         <v>0.02406875789165497</v>
       </c>
       <c r="E169" s="0">
@@ -24284,7 +24284,7 @@
       <c r="C170" s="0" t="n">
         <v>0.367</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="0" t="n">
         <v>0.02440095134079456</v>
       </c>
       <c r="E170" s="0">
@@ -24319,7 +24319,7 @@
       <c r="C171" s="0" t="n">
         <v>0.365</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="0" t="n">
         <v>0.02434027567505836</v>
       </c>
       <c r="E171" s="0">
@@ -24354,7 +24354,7 @@
       <c r="C172" s="0" t="n">
         <v>0.362</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="0" t="n">
         <v>0.02376594208180904</v>
       </c>
       <c r="E172" s="0">
@@ -24389,7 +24389,7 @@
       <c r="C173" s="0" t="n">
         <v>0.361</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="0" t="n">
         <v>0.02431243099272251</v>
       </c>
       <c r="E173" s="0">
@@ -24424,7 +24424,7 @@
       <c r="C174" s="0" t="n">
         <v>0.358</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="0" t="n">
         <v>0.02424491569399834</v>
       </c>
       <c r="E174" s="0">
@@ -24459,7 +24459,7 @@
       <c r="C175" s="0" t="n">
         <v>0.356</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="0" t="n">
         <v>0.02432944253087044</v>
       </c>
       <c r="E175" s="0">
@@ -24494,7 +24494,7 @@
       <c r="C176" s="0" t="n">
         <v>0.354</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="0" t="n">
         <v>0.02473657205700874</v>
       </c>
       <c r="E176" s="0">
@@ -24529,7 +24529,7 @@
       <c r="C177" s="0" t="n">
         <v>0.352</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="0" t="n">
         <v>0.02427547425031662</v>
       </c>
       <c r="E177" s="0">
@@ -24564,7 +24564,7 @@
       <c r="C178" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.02418882772326469</v>
       </c>
       <c r="E178" s="0">
@@ -24599,7 +24599,7 @@
       <c r="C179" s="0" t="n">
         <v>0.348</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="0" t="n">
         <v>0.0245915874838829</v>
       </c>
       <c r="E179" s="0">
@@ -24634,7 +24634,7 @@
       <c r="C180" s="0" t="n">
         <v>0.346</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="0" t="n">
         <v>0.02487228251993656</v>
       </c>
       <c r="E180" s="0">
@@ -24669,7 +24669,7 @@
       <c r="C181" s="0" t="n">
         <v>0.343</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="0" t="n">
         <v>0.02499474212527275</v>
       </c>
       <c r="E181" s="0">
@@ -24704,7 +24704,7 @@
       <c r="C182" s="0" t="n">
         <v>0.341</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="0" t="n">
         <v>0.02505173347890377</v>
       </c>
       <c r="E182" s="0">
@@ -24739,7 +24739,7 @@
       <c r="C183" s="0" t="n">
         <v>0.339</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="0" t="n">
         <v>0.02456580474972725</v>
       </c>
       <c r="E183" s="0">
@@ -24774,7 +24774,7 @@
       <c r="C184" s="0" t="n">
         <v>0.337</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="0" t="n">
         <v>0.02429625019431114</v>
       </c>
       <c r="E184" s="0">
@@ -24809,7 +24809,7 @@
       <c r="C185" s="0" t="n">
         <v>0.335</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185" s="0" t="n">
         <v>0.02401648834347725</v>
       </c>
       <c r="E185" s="0">
@@ -24844,7 +24844,7 @@
       <c r="C186" s="0" t="n">
         <v>0.333</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="0" t="n">
         <v>0.0249500460922718</v>
       </c>
       <c r="E186" s="0">
@@ -24879,7 +24879,7 @@
       <c r="C187" s="0" t="n">
         <v>0.33</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="0" t="n">
         <v>0.02474693581461906</v>
       </c>
       <c r="E187" s="0">
@@ -24914,7 +24914,7 @@
       <c r="C188" s="0" t="n">
         <v>0.328</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="0" t="n">
         <v>0.0247977115213871</v>
       </c>
       <c r="E188" s="0">
@@ -24949,7 +24949,7 @@
       <c r="C189" s="0" t="n">
         <v>0.327</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" s="0" t="n">
         <v>0.02455391362309456</v>
       </c>
       <c r="E189" s="0">
@@ -24984,7 +24984,7 @@
       <c r="C190" s="0" t="n">
         <v>0.324</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="0" t="n">
         <v>0.02486999705433846</v>
       </c>
       <c r="E190" s="0">
@@ -25019,7 +25019,7 @@
       <c r="C191" s="0" t="n">
         <v>0.322</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="0" t="n">
         <v>0.02434824593365192</v>
       </c>
       <c r="E191" s="0">
@@ -25054,7 +25054,7 @@
       <c r="C192" s="0" t="n">
         <v>0.32</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="0" t="n">
         <v>0.02544496022164822</v>
       </c>
       <c r="E192" s="0">
@@ -25089,7 +25089,7 @@
       <c r="C193" s="0" t="n">
         <v>0.317</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="0" t="n">
         <v>0.02464304119348526</v>
       </c>
       <c r="E193" s="0">
@@ -25124,7 +25124,7 @@
       <c r="C194" s="0" t="n">
         <v>0.315</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E194" s="0">
@@ -25159,7 +25159,7 @@
       <c r="C195" s="0" t="n">
         <v>0.313</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E195" s="0">
@@ -25194,7 +25194,7 @@
       <c r="C196" s="0" t="n">
         <v>0.311</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E196" s="0">
@@ -25228,7 +25228,7 @@
       <c r="C197" s="0" t="n">
         <v>0.309</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E197" s="0">
@@ -25262,7 +25262,7 @@
       <c r="C198" s="0" t="n">
         <v>0.306</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E198" s="0">
@@ -25296,7 +25296,7 @@
       <c r="C199" s="0" t="n">
         <v>0.304</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E199" s="0">
@@ -25330,7 +25330,7 @@
       <c r="C200" s="0" t="n">
         <v>0.301</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E200" s="0">
@@ -25364,7 +25364,7 @@
       <c r="C201" s="0" t="n">
         <v>0.299</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E201" s="0">
@@ -25398,7 +25398,7 @@
       <c r="C202" s="0" t="n">
         <v>0.297</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E202" s="0">
@@ -25432,7 +25432,7 @@
       <c r="C203" s="0" t="n">
         <v>0.295</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E203" s="0">
@@ -25466,7 +25466,7 @@
       <c r="C204" s="0" t="n">
         <v>0.293</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E204" s="0">
@@ -25500,7 +25500,7 @@
       <c r="C205" s="0" t="n">
         <v>0.291</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E205" s="0">
@@ -25534,7 +25534,7 @@
       <c r="C206" s="0" t="n">
         <v>0.288</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E206" s="0">
@@ -25568,7 +25568,7 @@
       <c r="C207" s="0" t="n">
         <v>0.286</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E207" s="0">
@@ -25602,7 +25602,7 @@
       <c r="C208" s="0" t="n">
         <v>0.284</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E208" s="0">
@@ -25636,7 +25636,7 @@
       <c r="C209" s="0" t="n">
         <v>0.282</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E209" s="0">
@@ -25670,7 +25670,7 @@
       <c r="C210" s="0" t="n">
         <v>0.279</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E210" s="0">
@@ -25704,7 +25704,7 @@
       <c r="C211" s="0" t="n">
         <v>0.277</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E211" s="0">
@@ -25738,7 +25738,7 @@
       <c r="C212" s="0" t="n">
         <v>0.275</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E212" s="0">
@@ -25772,7 +25772,7 @@
       <c r="C213" s="0" t="n">
         <v>0.272</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E213" s="0">
@@ -25806,7 +25806,7 @@
       <c r="C214" s="0" t="n">
         <v>0.27</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E214" s="0">
@@ -25840,7 +25840,7 @@
       <c r="C215" s="0" t="n">
         <v>0.268</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E215" s="0">
@@ -25874,7 +25874,7 @@
       <c r="C216" s="0" t="n">
         <v>0.265</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E216" s="0">
@@ -25908,7 +25908,7 @@
       <c r="C217" s="0" t="n">
         <v>0.263</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E217" s="0">
@@ -25942,7 +25942,7 @@
       <c r="C218" s="0" t="n">
         <v>0.261</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E218" s="0">
@@ -25976,7 +25976,7 @@
       <c r="C219" s="0" t="n">
         <v>0.259</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E219" s="0">
@@ -26010,7 +26010,7 @@
       <c r="C220" s="0" t="n">
         <v>0.256</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E220" s="0">
@@ -26044,7 +26044,7 @@
       <c r="C221" s="0" t="n">
         <v>0.254</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E221" s="0">
@@ -26078,7 +26078,7 @@
       <c r="C222" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E222" s="0">
@@ -26112,7 +26112,7 @@
       <c r="C223" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E223" s="0">
